--- a/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-07-28 01:47</t>
+    <t xml:space="preserve">2026-08-17 19:58</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-17 19:58</t>
+    <t xml:space="preserve">2026-09-01 17:46</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
+++ b/output/graficos_dimensiones/comunal_d_env_a_2018_nuble.xlsx
@@ -105,7 +105,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-01 17:46</t>
+    <t xml:space="preserve">2026-09-06 22:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
